--- a/data/Data_v11.xlsx
+++ b/data/Data_v11.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{336BA00A-2929-354D-ADF5-F5748977C271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99C8556-D097-2D43-B5AE-6DF767CED53B}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{336BA00A-2929-354D-ADF5-F5748977C271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EACD488-0FCC-EA49-A065-EE33A962B4D2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17060" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="780" windowWidth="29400" windowHeight="17060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario1" sheetId="1" r:id="rId1"/>
     <sheet name="scenario1cbam" sheetId="2" r:id="rId2"/>
     <sheet name="scenario2" sheetId="3" r:id="rId3"/>
     <sheet name="scenario2cbam" sheetId="4" r:id="rId4"/>
-    <sheet name="scenariocomparison" sheetId="11" r:id="rId5"/>
+    <sheet name="etc" sheetId="11" r:id="rId5"/>
     <sheet name="raw data1" sheetId="5" r:id="rId6"/>
     <sheet name="raw data1cbam" sheetId="6" r:id="rId7"/>
     <sheet name="raw data2" sheetId="7" r:id="rId8"/>
@@ -1294,7 +1294,7 @@
             <c:numRef>
               <c:f>'raw data1'!$G$6:$G$31</c:f>
               <c:numCache>
-                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1318,61 +1318,61 @@
                   <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18014987.510407992</c:v>
+                  <c:v>36000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5072,79 +5072,79 @@
       </c>
       <c r="I3" s="3">
         <f>VLOOKUP(I1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>16918935.862647582</v>
+        <v>18018107.885961488</v>
       </c>
       <c r="J3" s="3">
         <f>VLOOKUP(J1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>26466528.715745609</v>
+        <v>27615663.103755601</v>
       </c>
       <c r="K3" s="3">
         <f>VLOOKUP(K1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>27617247.355560631</v>
+        <v>28816344.108266711</v>
       </c>
       <c r="L3" s="3">
         <f>VLOOKUP(L1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>39608540.250578359</v>
+        <v>40857599.367980525</v>
       </c>
       <c r="M3" s="3">
         <f>VLOOKUP(M1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>47538588.013118297</v>
+        <v>48787647.130520463</v>
       </c>
       <c r="N3" s="3">
         <f>VLOOKUP(N1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="O3" s="3">
         <f>VLOOKUP(O1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="P3" s="3">
         <f>VLOOKUP(P1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
       <c r="Q3" s="3">
         <f>VLOOKUP(Q1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>60554170.440277562</v>
+        <v>61803229.557679728</v>
       </c>
       <c r="R3" s="3">
         <f>VLOOKUP(R1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>60554170.440277562</v>
+        <v>61803229.557679728</v>
       </c>
       <c r="S3" s="3">
         <f>VLOOKUP(S1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>67271205.29471153</v>
+        <v>68520264.412113696</v>
       </c>
       <c r="T3" s="3">
         <f>VLOOKUP(T1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>67271205.29471153</v>
+        <v>68520264.412113696</v>
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>62337025.930106372</v>
+        <v>63586085.047508538</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>62337025.930106372</v>
+        <v>63586085.047508538</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="X3" s="3">
         <f>VLOOKUP(X1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="Y3" s="3">
         <f>VLOOKUP(Y1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="Z3" s="3">
         <f>VLOOKUP(Z1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
       <c r="AA3" s="3">
         <f>VLOOKUP(AA1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>79098584.68098636</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15288,7 +15288,7 @@
       <c r="F6" s="21">
         <v>0</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="28">
         <v>0</v>
       </c>
       <c r="H6" s="21">
@@ -15343,7 +15343,7 @@
       <c r="F7" s="21">
         <v>0</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="28">
         <v>15000000</v>
       </c>
       <c r="H7" s="21">
@@ -15407,7 +15407,7 @@
       <c r="F8" s="21">
         <v>0</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="28">
         <v>30000000</v>
       </c>
       <c r="H8" s="21">
@@ -15471,7 +15471,7 @@
       <c r="F9" s="21">
         <v>0</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="28">
         <v>30000000</v>
       </c>
       <c r="H9" s="21">
@@ -15535,7 +15535,7 @@
       <c r="F10" s="21">
         <v>0</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="28">
         <v>36000000</v>
       </c>
       <c r="H10" s="21">
@@ -15599,7 +15599,7 @@
       <c r="F11" s="21">
         <v>57598122.732788444</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="28">
         <v>36000000</v>
       </c>
       <c r="H11" s="21">
@@ -15663,7 +15663,7 @@
       <c r="F12" s="21">
         <v>57598122.732788444</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="28">
         <v>36000000</v>
       </c>
       <c r="H12" s="21">
@@ -15727,12 +15727,12 @@
       <c r="F13" s="21">
         <v>34554528.524486057</v>
       </c>
-      <c r="G13" s="21">
-        <v>18014987.510407992</v>
+      <c r="G13" s="28">
+        <v>36000000</v>
       </c>
       <c r="H13" s="21">
         <f t="shared" si="1"/>
-        <v>603912845.40093946</v>
+        <v>621897857.89053142</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="P13" s="22">
         <f>(G13+F13)*parameters!$C$7*parameters!L14/1000</f>
-        <v>3212838.5419885847</v>
+        <v>4312010.5653024903</v>
       </c>
       <c r="Q13" s="22">
         <f>E13*parameters!$E$7*parameters!$D$7*parameters!L14/1000</f>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="R13" s="24">
         <f t="shared" si="2"/>
-        <v>16918935.862647582</v>
+        <v>18018107.885961488</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15791,12 +15791,12 @@
       <c r="F14" s="21">
         <v>58032936.528446592</v>
       </c>
-      <c r="G14" s="21">
-        <v>18014987.510407992</v>
+      <c r="G14" s="28">
+        <v>36000000</v>
       </c>
       <c r="H14" s="21">
         <f t="shared" si="1"/>
-        <v>608670888.73670208</v>
+        <v>626655901.22629404</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="P14" s="22">
         <f>(G14+F14)*parameters!$C$7*parameters!L15/1000</f>
-        <v>4859006.0585385747</v>
+        <v>6008140.4465485672</v>
       </c>
       <c r="Q14" s="22">
         <f>E14*parameters!$E$7*parameters!$D$7*parameters!L15/1000</f>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="R14" s="24">
         <f t="shared" si="2"/>
-        <v>26466528.715745609</v>
+        <v>27615663.103755601</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15855,12 +15855,12 @@
       <c r="F15" s="21">
         <v>58032936.528446592</v>
       </c>
-      <c r="G15" s="21">
-        <v>18014987.510407992</v>
+      <c r="G15" s="28">
+        <v>36000000</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="1"/>
-        <v>608670888.73670208</v>
+        <v>626655901.22629404</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="P15" s="22">
         <f>(G15+F15)*parameters!$C$7*parameters!L16/1000</f>
-        <v>5070267.1915185126</v>
+        <v>6269363.9442245914</v>
       </c>
       <c r="Q15" s="22">
         <f>E15*parameters!$E$7*parameters!$D$7*parameters!L16/1000</f>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="R15" s="24">
         <f t="shared" si="2"/>
-        <v>27617247.355560631</v>
+        <v>28816344.108266711</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15919,12 +15919,12 @@
       <c r="F16" s="21">
         <v>87753799.493795186</v>
       </c>
-      <c r="G16" s="21">
-        <v>18014987.510407992</v>
+      <c r="G16" s="28">
+        <v>36000000</v>
       </c>
       <c r="H16" s="21">
         <f t="shared" si="1"/>
-        <v>614694003.84491277</v>
+        <v>632679016.33450472</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="P16" s="22">
         <f>(G16+F16)*parameters!$C$7*parameters!L17/1000</f>
-        <v>7345642.2574419109</v>
+        <v>8594701.3748440761</v>
       </c>
       <c r="Q16" s="22">
         <f>E16*parameters!$E$7*parameters!$D$7*parameters!L17/1000</f>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="R16" s="24">
         <f t="shared" si="2"/>
-        <v>39608540.250578359</v>
+        <v>40857599.367980525</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -15983,12 +15983,12 @@
       <c r="F17" s="21">
         <v>107261988.8907399</v>
       </c>
-      <c r="G17" s="21">
-        <v>18014987.510407992</v>
+      <c r="G17" s="28">
+        <v>36000000</v>
       </c>
       <c r="H17" s="21">
         <f t="shared" si="1"/>
-        <v>618647458.03726149</v>
+        <v>636632470.52685344</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="P17" s="22">
         <f>(G17+F17)*parameters!$C$7*parameters!L18/1000</f>
-        <v>8700486.0110597238</v>
+        <v>9949545.1284618881</v>
       </c>
       <c r="Q17" s="22">
         <f>E17*parameters!$E$7*parameters!$D$7*parameters!L18/1000</f>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="R17" s="24">
         <f t="shared" si="2"/>
-        <v>47538588.013118297</v>
+        <v>48787647.130520463</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16047,12 +16047,12 @@
       <c r="F18" s="21">
         <v>124316161.1166027</v>
       </c>
-      <c r="G18" s="21">
-        <v>18014987.510407992</v>
+      <c r="G18" s="28">
+        <v>36000000</v>
       </c>
       <c r="H18" s="21">
         <f t="shared" si="1"/>
-        <v>622103590.60351229</v>
+        <v>640088603.09310424</v>
       </c>
       <c r="I18" s="22"/>
       <c r="J18" s="22">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="P18" s="22">
         <f>(G18+F18)*parameters!$C$7*parameters!L19/1000</f>
-        <v>9884898.2721458934</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q18" s="22">
         <f>E18*parameters!$E$7*parameters!$D$7*parameters!L19/1000</f>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="R18" s="24">
         <f t="shared" si="2"/>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16111,12 +16111,12 @@
       <c r="F19" s="21">
         <v>124316161.1166027</v>
       </c>
-      <c r="G19" s="21">
-        <v>18014987.510407992</v>
+      <c r="G19" s="28">
+        <v>36000000</v>
       </c>
       <c r="H19" s="21">
         <f t="shared" si="1"/>
-        <v>622103590.60351229</v>
+        <v>640088603.09310424</v>
       </c>
       <c r="I19" s="22"/>
       <c r="J19" s="22">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="P19" s="22">
         <f>(G19+F19)*parameters!$C$7*parameters!L20/1000</f>
-        <v>9884898.2721458934</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q19" s="22">
         <f>E19*parameters!$E$7*parameters!$D$7*parameters!L20/1000</f>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="R19" s="24">
         <f t="shared" si="2"/>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16175,12 +16175,12 @@
       <c r="F20" s="21">
         <v>124316161.1166027</v>
       </c>
-      <c r="G20" s="21">
-        <v>18014987.510407992</v>
+      <c r="G20" s="28">
+        <v>36000000</v>
       </c>
       <c r="H20" s="21">
         <f t="shared" si="1"/>
-        <v>622103590.60351229</v>
+        <v>640088603.09310424</v>
       </c>
       <c r="I20" s="22"/>
       <c r="J20" s="22">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="P20" s="22">
         <f>(G20+F20)*parameters!$C$7*parameters!L21/1000</f>
-        <v>9884898.2721458934</v>
+        <v>11133957.38954806</v>
       </c>
       <c r="Q20" s="22">
         <f>E20*parameters!$E$7*parameters!$D$7*parameters!L21/1000</f>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="R20" s="24">
         <f t="shared" si="2"/>
-        <v>54469027.009193808</v>
+        <v>55718086.126595974</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16239,12 +16239,12 @@
       <c r="F21" s="21">
         <v>139288136.23201731</v>
       </c>
-      <c r="G21" s="21">
-        <v>18014987.510407992</v>
+      <c r="G21" s="28">
+        <v>36000000</v>
       </c>
       <c r="H21" s="21">
         <f t="shared" si="1"/>
-        <v>625137753.15870285</v>
+        <v>643122765.64829481</v>
       </c>
       <c r="I21" s="22"/>
       <c r="J21" s="22">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="P21" s="22">
         <f>(G21+F21)*parameters!$C$7*parameters!L22/1000</f>
-        <v>10924701.943911437</v>
+        <v>12173761.061313603</v>
       </c>
       <c r="Q21" s="22">
         <f>E21*parameters!$E$7*parameters!$D$7*parameters!L22/1000</f>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="R21" s="24">
         <f t="shared" si="2"/>
-        <v>60554170.440277562</v>
+        <v>61803229.557679728</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16303,12 +16303,12 @@
       <c r="F22" s="21">
         <v>139288136.23201731</v>
       </c>
-      <c r="G22" s="21">
-        <v>18014987.510407992</v>
+      <c r="G22" s="28">
+        <v>36000000</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="1"/>
-        <v>625137753.15870285</v>
+        <v>643122765.64829481</v>
       </c>
       <c r="I22" s="22"/>
       <c r="J22" s="22">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="P22" s="22">
         <f>(G22+F22)*parameters!$C$7*parameters!L23/1000</f>
-        <v>10924701.943911437</v>
+        <v>12173761.061313603</v>
       </c>
       <c r="Q22" s="22">
         <f>E22*parameters!$E$7*parameters!$D$7*parameters!L23/1000</f>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="R22" s="24">
         <f t="shared" si="2"/>
-        <v>60554170.440277562</v>
+        <v>61803229.557679728</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16367,12 +16367,12 @@
       <c r="F23" s="21">
         <v>155813497.17487901</v>
       </c>
-      <c r="G23" s="21">
-        <v>18014987.510407992</v>
+      <c r="G23" s="28">
+        <v>36000000</v>
       </c>
       <c r="H23" s="21">
         <f t="shared" si="1"/>
-        <v>628486718.87613964</v>
+        <v>646471731.3657316</v>
       </c>
       <c r="I23" s="22"/>
       <c r="J23" s="22">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="P23" s="22">
         <f>(G23+F23)*parameters!$C$7*parameters!L24/1000</f>
-        <v>12072388.261393182</v>
+        <v>13321447.378795348</v>
       </c>
       <c r="Q23" s="22">
         <f>E23*parameters!$E$7*parameters!$D$7*parameters!L24/1000</f>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="R23" s="24">
         <f t="shared" si="2"/>
-        <v>67271205.29471153</v>
+        <v>68520264.412113696</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16431,12 +16431,12 @@
       <c r="F24" s="21">
         <v>155813497.17487901</v>
       </c>
-      <c r="G24" s="21">
-        <v>18014987.510407992</v>
+      <c r="G24" s="28">
+        <v>36000000</v>
       </c>
       <c r="H24" s="21">
         <f t="shared" si="1"/>
-        <v>628486718.87613964</v>
+        <v>646471731.3657316</v>
       </c>
       <c r="I24" s="22"/>
       <c r="J24" s="22">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="P24" s="22">
         <f>(G24+F24)*parameters!$C$7*parameters!L25/1000</f>
-        <v>12072388.261393182</v>
+        <v>13321447.378795348</v>
       </c>
       <c r="Q24" s="22">
         <f>E24*parameters!$E$7*parameters!$D$7*parameters!L25/1000</f>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="R24" s="24">
         <f t="shared" si="2"/>
-        <v>67271205.29471153</v>
+        <v>68520264.412113696</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16495,12 +16495,12 @@
       <c r="F25" s="21">
         <v>171529117.18246049</v>
       </c>
-      <c r="G25" s="21">
-        <v>18014987.510407992</v>
+      <c r="G25" s="28">
+        <v>36000000</v>
       </c>
       <c r="H25" s="21">
         <f t="shared" si="1"/>
-        <v>631671585.62825644</v>
+        <v>649656598.1178484</v>
       </c>
       <c r="I25" s="22"/>
       <c r="J25" s="22">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
-        <v>13163838.070919717</v>
+        <v>14412897.188321883</v>
       </c>
       <c r="Q25" s="22">
         <f>E25*parameters!$E$7*parameters!$D$7*parameters!L26/1000</f>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="R25" s="24">
         <f t="shared" si="2"/>
-        <v>62337025.930106372</v>
+        <v>63586085.047508538</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16559,12 +16559,12 @@
       <c r="F26" s="21">
         <v>171529117.18246049</v>
       </c>
-      <c r="G26" s="21">
-        <v>18014987.510407992</v>
+      <c r="G26" s="28">
+        <v>36000000</v>
       </c>
       <c r="H26" s="21">
         <f t="shared" si="1"/>
-        <v>631671585.62825644</v>
+        <v>649656598.1178484</v>
       </c>
       <c r="I26" s="22"/>
       <c r="J26" s="22">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
-        <v>13163838.070919717</v>
+        <v>14412897.188321883</v>
       </c>
       <c r="Q26" s="22">
         <f>E26*parameters!$E$7*parameters!$D$7*parameters!L27/1000</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="R26" s="24">
         <f t="shared" si="2"/>
-        <v>62337025.930106372</v>
+        <v>63586085.047508538</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16623,12 +16623,12 @@
       <c r="F27" s="21">
         <v>184910526.84981459</v>
       </c>
-      <c r="G27" s="21">
-        <v>18014987.510407992</v>
+      <c r="G27" s="28">
+        <v>36000000</v>
       </c>
       <c r="H27" s="21">
         <f t="shared" si="1"/>
-        <v>634383410.34312332</v>
+        <v>652368422.83271527</v>
       </c>
       <c r="I27" s="22"/>
       <c r="J27" s="22">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="P27" s="22">
         <f>(G27+F27)*parameters!$C$7*parameters!L28/1000</f>
-        <v>14093176.972317459</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q27" s="22">
         <f>E27*parameters!$E$7*parameters!$D$7*parameters!L28/1000</f>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="R27" s="24">
         <f t="shared" si="2"/>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16687,12 +16687,12 @@
       <c r="F28" s="21">
         <v>184910526.84981459</v>
       </c>
-      <c r="G28" s="21">
-        <v>18014987.510407992</v>
+      <c r="G28" s="28">
+        <v>36000000</v>
       </c>
       <c r="H28" s="21">
         <f t="shared" si="1"/>
-        <v>634383410.34312332</v>
+        <v>652368422.83271527</v>
       </c>
       <c r="I28" s="22"/>
       <c r="J28" s="22">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="P28" s="22">
         <f>(G28+F28)*parameters!$C$7*parameters!L29/1000</f>
-        <v>14093176.972317459</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q28" s="22">
         <f>E28*parameters!$E$7*parameters!$D$7*parameters!L29/1000</f>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="R28" s="24">
         <f t="shared" si="2"/>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16751,12 +16751,12 @@
       <c r="F29" s="21">
         <v>184910526.84981459</v>
       </c>
-      <c r="G29" s="21">
-        <v>18014987.510407992</v>
+      <c r="G29" s="28">
+        <v>36000000</v>
       </c>
       <c r="H29" s="21">
         <f t="shared" si="1"/>
-        <v>634383410.34312332</v>
+        <v>652368422.83271527</v>
       </c>
       <c r="I29" s="22"/>
       <c r="J29" s="22">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="P29" s="22">
         <f>(G29+F29)*parameters!$C$7*parameters!L30/1000</f>
-        <v>14093176.972317459</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q29" s="22">
         <f>E29*parameters!$E$7*parameters!$D$7*parameters!L30/1000</f>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="R29" s="24">
         <f t="shared" si="2"/>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16815,12 +16815,12 @@
       <c r="F30" s="21">
         <v>184910526.84981459</v>
       </c>
-      <c r="G30" s="21">
-        <v>18014987.510407992</v>
+      <c r="G30" s="28">
+        <v>36000000</v>
       </c>
       <c r="H30" s="21">
         <f t="shared" si="1"/>
-        <v>634383410.34312332</v>
+        <v>652368422.83271527</v>
       </c>
       <c r="I30" s="22"/>
       <c r="J30" s="22">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="P30" s="22">
         <f>(G30+F30)*parameters!$C$7*parameters!L31/1000</f>
-        <v>14093176.972317459</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q30" s="22">
         <f>E30*parameters!$E$7*parameters!$D$7*parameters!L31/1000</f>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="R30" s="24">
         <f t="shared" si="2"/>
-        <v>79098584.680986345</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16879,12 +16879,12 @@
       <c r="F31" s="21">
         <v>184910526.84981459</v>
       </c>
-      <c r="G31" s="21">
-        <v>18014987.510407992</v>
+      <c r="G31" s="28">
+        <v>36000000</v>
       </c>
       <c r="H31" s="21">
         <f t="shared" si="1"/>
-        <v>634383410.34312332</v>
+        <v>652368422.83271527</v>
       </c>
       <c r="I31" s="22"/>
       <c r="J31" s="22">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="P31" s="22">
         <f>(G31+F31)*parameters!$C$7*parameters!L32/1000</f>
-        <v>14093176.972317459</v>
+        <v>15342236.089719623</v>
       </c>
       <c r="Q31" s="22">
         <f>E31*parameters!$E$7*parameters!$D$7*parameters!L32/1000</f>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="R31" s="27">
         <f t="shared" si="2"/>
-        <v>79098584.68098636</v>
+        <v>80347643.798388511</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/data/Data_v11.xlsx
+++ b/data/Data_v11.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/00_플랜잇_철강inputoutput연구/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{336BA00A-2929-354D-ADF5-F5748977C271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EACD488-0FCC-EA49-A065-EE33A962B4D2}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{336BA00A-2929-354D-ADF5-F5748977C271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{487D0F2B-D89F-6246-9265-251A0C979228}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="780" windowWidth="29400" windowHeight="17060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="17060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="scenario1" sheetId="1" r:id="rId1"/>
-    <sheet name="scenario1cbam" sheetId="2" r:id="rId2"/>
-    <sheet name="scenario2" sheetId="3" r:id="rId3"/>
-    <sheet name="scenario2cbam" sheetId="4" r:id="rId4"/>
+    <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
+    <sheet name="Scenario1CBAM" sheetId="2" r:id="rId2"/>
+    <sheet name="Scenario2" sheetId="3" r:id="rId3"/>
+    <sheet name="Scenario2CBAM" sheetId="4" r:id="rId4"/>
     <sheet name="etc" sheetId="11" r:id="rId5"/>
     <sheet name="raw data1" sheetId="5" r:id="rId6"/>
     <sheet name="raw data1cbam" sheetId="6" r:id="rId7"/>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>63586085.047508538</v>
+        <v>74908016.63464345</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data1'!$A$6:$R$31,18)</f>
-        <v>63586085.047508538</v>
+        <v>74908016.63464345</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data1'!$A$6:$R$31,18)</f>
@@ -7051,7 +7051,7 @@
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
       <c r="H26" s="35">
-        <v>0.627</v>
+        <v>6.2700000000000006E-2</v>
       </c>
       <c r="I26" s="36">
         <v>0.39333333333333337</v>
@@ -7077,7 +7077,7 @@
       <c r="F27" s="35"/>
       <c r="G27" s="35"/>
       <c r="H27" s="35">
-        <v>0.627</v>
+        <v>6.2700000000000006E-2</v>
       </c>
       <c r="I27" s="36">
         <v>0.35</v>
@@ -9922,11 +9922,11 @@
       </c>
       <c r="U3" s="3">
         <f>VLOOKUP(U1,'raw data1cbam'!$A$6:$R$31,18)</f>
-        <v>63575977.794004813</v>
+        <v>74897909.381139725</v>
       </c>
       <c r="V3" s="3">
         <f>VLOOKUP(V1,'raw data1cbam'!$A$6:$R$31,18)</f>
-        <v>63575977.794004813</v>
+        <v>74897909.381139725</v>
       </c>
       <c r="W3" s="3">
         <f>VLOOKUP(W1,'raw data1cbam'!$A$6:$R$31,18)</f>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$H26)*parameters!L26/1000</f>
-        <v>7483750.6326445509</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="R25" s="24">
         <f t="shared" si="2"/>
-        <v>63586085.047508538</v>
+        <v>74908016.63464345</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$H27)*parameters!L27/1000</f>
-        <v>7483750.6326445509</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="R26" s="24">
         <f t="shared" si="2"/>
-        <v>63586085.047508538</v>
+        <v>74908016.63464345</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="O25" s="22">
         <f>parameters!$G$7*(1-parameters!$H26)*parameters!L26/1000</f>
-        <v>7483750.6326445509</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P25" s="22">
         <f>(G25+F25)*parameters!$C$7*parameters!L26/1000</f>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="R25" s="24">
         <f t="shared" si="2"/>
-        <v>63575977.794004813</v>
+        <v>74897909.381139725</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19400,7 +19400,7 @@
       </c>
       <c r="O26" s="22">
         <f>parameters!$G$7*(1-parameters!$H27)*parameters!L27/1000</f>
-        <v>7483750.6326445509</v>
+        <v>18805682.219779458</v>
       </c>
       <c r="P26" s="22">
         <f>(G26+F26)*parameters!$C$7*parameters!L27/1000</f>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="R26" s="24">
         <f t="shared" si="2"/>
-        <v>63575977.794004813</v>
+        <v>74897909.381139725</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
